--- a/public/crawlability-talentsolutions-september-2026.xlsx
+++ b/public/crawlability-talentsolutions-september-2026.xlsx
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -504,7 +504,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>להסיר ממפת האתר כתובת אחת שמחזירה שגיאה, או לתקן את העמוד.</t>
+          <t>כתובת אחת במפת האתר נמצאת בלולאת הפניות; לתקן את כלל ההפניה ולהסיר מהמפה עד לתיקון.</t>
         </is>
       </c>
     </row>
@@ -519,7 +519,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>כתובות שבורות (404): כתובת אחת (הבולטת: https://talentsolutions.manpowergroup.co.il/wp-content/uploads/2022/07/אורנה_2_פ, 0 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>לולאות הפניה: 2 כתובות (הבולטת: https://talentsolutions.manpowergroup.co.il/careers/, 39 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
         </is>
       </c>
     </row>
@@ -527,14 +527,14 @@
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>גבוהה</t>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>בינונית</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>לולאות הפניה: 2 כתובות (הבולטת: https://talentsolutions.manpowergroup.co.il/careers/, 39 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>5 כתובות במפת האתר חסומות ב-robots.txt; להסיר מהמפה או לפתוח לסריקה.</t>
         </is>
       </c>
     </row>
@@ -549,7 +549,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5 כתובות במפת האתר חסומות ב-robots.txt; להסיר מהמפה או לפתוח לסריקה.</t>
+          <t>קישורים שגויים בתבנית (javaScript(0);): 78 כתובות (הבולטת: https://talentsolutions.manpowergroup.co.il/javaScript(0);, 4 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
         </is>
       </c>
     </row>
@@ -564,7 +564,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>קישורים שגויים בתבנית (javaScript(0);): 39 כתובות (הבולטת: https://talentsolutions.manpowergroup.co.il/javaScript(0);, 4 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>קישורים עם רווח בסוף הכתובת: 3 כתובות (הבולטת: https://talentsolutions.manpowergroup.co.il/manageandoptimize/ [רווח בסוף], 79 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
         </is>
       </c>
     </row>
@@ -609,7 +609,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>קישורים פנימיים לכתובות שמפנות (301/308): 63 כתובות (הבולטת: https://talentsolutions.manpowergroup.co.il/operationalexcellence/, 80 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>קישורים פנימיים לכתובות שמפנות (301/308): 23 כתובות (הבולטת: https://talentsolutions.manpowergroup.co.il/operationalexcellence/, 80 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
         </is>
       </c>
     </row>
@@ -617,14 +617,14 @@
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>בינונית</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>quest.manpowergroup.co.il: להגדיר noindex (כתובת אחת באינדקס).</t>
+          <t>קישורים פנימיים ללא לוכסן סופי: כתובת אחת (הבולטת: https://talentsolutions.manpowergroup.co.il/blog, 78 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>קישורים פנימיים ללא לוכסן סופי: 4 כתובות (הבולטת: https://talentsolutions.manpowergroup.co.il/manageandoptimize/ , 79 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>quest.manpowergroup.co.il: להגדיר noindex (כתובת אחת באינדקס).</t>
         </is>
       </c>
     </row>
@@ -653,6 +653,21 @@
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>כתובות שבורות (404): כתובת אחת (הבולטת: https://talentsolutions.manpowergroup.co.il/wp-content/uploads/2022/07/אורנה_2_פ…, 0 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>להריץ מחדש את ה-Website Audit של talentsolutions ב-SE Ranking (הסריקה האחרונה: 2026-05-25); הפעלה מחדש דרך ה-API אינה זמינה בחשבון, יש להפעיל בממשק.</t>
         </is>
@@ -1145,7 +1160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K68"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -2447,7 +2462,7 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>https://talentsolutions.manpowergroup.co.il/javaScript(0</t>
+          <t>https://talentsolutions.manpowergroup.co.il/blog</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
@@ -2460,1896 +2475,16 @@
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
+          <t>https://talentsolutions.manpowergroup.co.il/blog/</t>
         </is>
       </c>
       <c r="E25" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>קישורים פנימיים לכתובות שמפנות (301/308)</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). קישור פנימי לכתובת שמפנה (301). לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
-        </is>
-      </c>
-      <c r="J25" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="K25" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/?page_id=1212</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="n">
-        <v>301</v>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>301 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D26" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>קישורים פנימיים לכתובות שמפנות (301/308)</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). קישור פנימי לכתובת שמפנה (301). לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
-        </is>
-      </c>
-      <c r="J26" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="K26" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/contact/javaScript(0</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="n">
-        <v>301</v>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>301 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>קישורים פנימיים לכתובות שמפנות (301/308)</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). קישור פנימי לכתובת שמפנה (301). לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
-        </is>
-      </c>
-      <c r="J27" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="K27" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/about-us/javaScript(0</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="n">
-        <v>301</v>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>301 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D28" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>קישורים פנימיים לכתובות שמפנות (301/308)</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). קישור פנימי לכתובת שמפנה (301). לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
-        </is>
-      </c>
-      <c r="J28" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="K28" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/rod-מול-end-to-end-rpo-איך-לבחור-את-המודל-הנכון-לארגו/javaScript(0</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="n">
-        <v>301</v>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>301 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>קישורים פנימיים לכתובות שמפנות (301/308)</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). קישור פנימי לכתובת שמפנה (301). לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
-        </is>
-      </c>
-      <c r="J29" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="K29" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/transform/javaScript(0</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="n">
-        <v>301</v>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>301 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>קישורים פנימיים לכתובות שמפנות (301/308)</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). קישור פנימי לכתובת שמפנה (301). לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
-        </is>
-      </c>
-      <c r="J30" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="K30" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/manageandoptimize/organizationalconsulting/javaScript(0</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="n">
-        <v>301</v>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>301 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>קישורים פנימיים לכתובות שמפנות (301/308)</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). קישור פנימי לכתובת שמפנה (301). לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
-        </is>
-      </c>
-      <c r="J31" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="K31" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/manageandoptimize/javaScript(0</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="n">
-        <v>301</v>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>301 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>קישורים פנימיים לכתובות שמפנות (301/308)</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). קישור פנימי לכתובת שמפנה (301). לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
-        </is>
-      </c>
-      <c r="J32" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="K32" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/manageandoptimize/operationalexcellence/javaScript(0</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="n">
-        <v>301</v>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>301 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D33" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>קישורים פנימיים לכתובות שמפנות (301/308)</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). קישור פנימי לכתובת שמפנה (301). לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
-        </is>
-      </c>
-      <c r="J33" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="K33" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/attract/rod/javaScript(0</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="n">
-        <v>301</v>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>301 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D34" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>קישורים פנימיים לכתובות שמפנות (301/308)</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). קישור פנימי לכתובת שמפנה (301). לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
-        </is>
-      </c>
-      <c r="J34" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="K34" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/attract/rpo/javaScript(0</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="n">
-        <v>301</v>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>301 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>קישורים פנימיים לכתובות שמפנות (301/308)</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). קישור פנימי לכתובת שמפנה (301). לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
-        </is>
-      </c>
-      <c r="J35" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="K35" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/תנאי-שימוש/javaScript(0</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="n">
-        <v>301</v>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>301 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>קישורים פנימיים לכתובות שמפנות (301/308)</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). קישור פנימי לכתובת שמפנה (301). לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
-        </is>
-      </c>
-      <c r="J36" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="K36" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/מדיניות-קוקיז/javaScript(0</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="n">
-        <v>301</v>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>301 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D37" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>קישורים פנימיים לכתובות שמפנות (301/308)</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). קישור פנימי לכתובת שמפנה (301). לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
-        </is>
-      </c>
-      <c r="J37" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="K37" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/ibm/javaScript(0</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="n">
-        <v>301</v>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>301 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D38" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>קישורים פנימיים לכתובות שמפנות (301/308)</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). קישור פנימי לכתובת שמפנה (301). לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
-        </is>
-      </c>
-      <c r="J38" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="K38" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/מדיניות-פרטיות/javaScript(0</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="n">
-        <v>301</v>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>301 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>קישורים פנימיים לכתובות שמפנות (301/308)</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). קישור פנימי לכתובת שמפנה (301). לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
-        </is>
-      </c>
-      <c r="J39" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="K39" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/retainanddevelop/javaScript(0</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="n">
-        <v>301</v>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>301 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D40" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>קישורים פנימיים לכתובות שמפנות (301/308)</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). קישור פנימי לכתובת שמפנה (301). לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
-        </is>
-      </c>
-      <c r="J40" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="K40" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/מה-זה-rpo-ב-60-שניות/javaScript(0</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="n">
-        <v>301</v>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>301 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D41" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>קישורים פנימיים לכתובות שמפנות (301/308)</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). קישור פנימי לכתובת שמפנה (301). לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
-        </is>
-      </c>
-      <c r="J41" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="K41" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/attract/market-intelligence/javaScript(0</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="n">
-        <v>301</v>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>301 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>קישורים פנימיים לכתובות שמפנות (301/308)</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). קישור פנימי לכתובת שמפנה (301). לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
-        </is>
-      </c>
-      <c r="J42" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="K42" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/retainanddevelop/developmentprograms/javaScript(0</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="n">
-        <v>301</v>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>301 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>קישורים פנימיים לכתובות שמפנות (301/308)</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). קישור פנימי לכתובת שמפנה (301). לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
-        </is>
-      </c>
-      <c r="J43" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="K43" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/about-us/msp/javaScript(0</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="n">
-        <v>301</v>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>301 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>קישורים פנימיים לכתובות שמפנות (301/308)</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). קישור פנימי לכתובת שמפנה (301). לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
-        </is>
-      </c>
-      <c r="J44" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="K44" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/ministry/javaScript(0</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="n">
-        <v>301</v>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>301 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D45" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>קישורים פנימיים לכתובות שמפנות (301/308)</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). קישור פנימי לכתובת שמפנה (301). לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
-        </is>
-      </c>
-      <c r="J45" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="K45" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/attract/javaScript(0</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="n">
-        <v>301</v>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>301 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D46" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>קישורים פנימיים לכתובות שמפנות (301/308)</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). קישור פנימי לכתובת שמפנה (301). לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
-        </is>
-      </c>
-      <c r="J46" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="K46" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/mistakes/javaScript(0</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="n">
-        <v>301</v>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>301 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D47" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>קישורים פנימיים לכתובות שמפנות (301/308)</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). קישור פנימי לכתובת שמפנה (301). לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
-        </is>
-      </c>
-      <c r="J47" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="K47" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/blog/javaScript(0</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="n">
-        <v>301</v>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>301 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D48" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>קישורים פנימיים לכתובות שמפנות (301/308)</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). קישור פנימי לכתובת שמפנה (301). לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
-        </is>
-      </c>
-      <c r="J48" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="K48" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/transform/professionaldevelopment/javaScript(0</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="n">
-        <v>301</v>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>301 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D49" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>קישורים פנימיים לכתובות שמפנות (301/308)</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). קישור פנימי לכתובת שמפנה (301). לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
-        </is>
-      </c>
-      <c r="J49" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="K49" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/טסט-8/javaScript(0</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="n">
-        <v>301</v>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>301 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D50" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>קישורים פנימיים לכתובות שמפנות (301/308)</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). קישור פנימי לכתובת שמפנה (301). לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
-        </is>
-      </c>
-      <c r="J50" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="K50" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/אתגרים-בגיוס-טאלנטים-להייטק-בישראל/javaScript(0</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="n">
-        <v>301</v>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>301 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D51" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>קישורים פנימיים לכתובות שמפנות (301/308)</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). קישור פנימי לכתובת שמפנה (301). לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
-        </is>
-      </c>
-      <c r="J51" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="K51" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/blog/page/2/javaScript(0</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="n">
-        <v>301</v>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>301 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D52" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>קישורים פנימיים לכתובות שמפנות (301/308)</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). קישור פנימי לכתובת שמפנה (301). לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
-        </is>
-      </c>
-      <c r="J52" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="K52" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/היתרונות-של-מיקור-החוץ-בתהליכי-גיוס/javaScript(0</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="n">
-        <v>301</v>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>301 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D53" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>קישורים פנימיים לכתובות שמפנות (301/308)</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). קישור פנימי לכתובת שמפנה (301). לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
-        </is>
-      </c>
-      <c r="J53" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="K53" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/attract/rpo-projects/javaScript(0</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="n">
-        <v>301</v>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>301 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D54" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>קישורים פנימיים לכתובות שמפנות (301/308)</t>
-        </is>
-      </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). קישור פנימי לכתובת שמפנה (301). לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
-        </is>
-      </c>
-      <c r="J54" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="K54" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/category/ללא-קטגוריה/javaScript(0</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="n">
-        <v>301</v>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>301 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D55" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>קישורים פנימיים לכתובות שמפנות (301/308)</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). קישור פנימי לכתובת שמפנה (301). לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
-        </is>
-      </c>
-      <c r="J55" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="K55" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/team/jonas-prising-6/javaScript(0</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="n">
-        <v>301</v>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>301 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D56" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>קישורים פנימיים לכתובות שמפנות (301/308)</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). קישור פנימי לכתובת שמפנה (301). לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
-        </is>
-      </c>
-      <c r="J56" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="K56" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/team/אינה-סרנגה/javaScript(0</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="n">
-        <v>301</v>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>301 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D57" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>קישורים פנימיים לכתובות שמפנות (301/308)</t>
-        </is>
-      </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). קישור פנימי לכתובת שמפנה (301). לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
-        </is>
-      </c>
-      <c r="J57" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="K57" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/team/אלכסנדרה-ויט/javaScript(0</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="n">
-        <v>301</v>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>301 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D58" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>קישורים פנימיים לכתובות שמפנות (301/308)</t>
-        </is>
-      </c>
-      <c r="I58" s="2" t="inlineStr">
-        <is>
-          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). קישור פנימי לכתובת שמפנה (301). לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
-        </is>
-      </c>
-      <c r="J58" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="K58" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/team/jonas-prising-7/javaScript(0</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="n">
-        <v>301</v>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>301 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D59" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>קישורים פנימיים לכתובות שמפנות (301/308)</t>
-        </is>
-      </c>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). קישור פנימי לכתובת שמפנה (301). לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
-        </is>
-      </c>
-      <c r="J59" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="K59" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/team/jonas-prising-8/javaScript(0</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="n">
-        <v>301</v>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>301 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D60" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>קישורים פנימיים לכתובות שמפנות (301/308)</t>
-        </is>
-      </c>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). קישור פנימי לכתובת שמפנה (301). לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
-        </is>
-      </c>
-      <c r="J60" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="K60" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/category/ללא-קטגוריה/page/2/javaScript(0</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="n">
-        <v>301</v>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>301 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D61" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F61" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>קישורים פנימיים לכתובות שמפנות (301/308)</t>
-        </is>
-      </c>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). קישור פנימי לכתובת שמפנה (301). לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
-        </is>
-      </c>
-      <c r="J61" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="K61" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/טסט-4/javaScript(0</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="n">
-        <v>301</v>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>301 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D62" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F62" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>קישורים פנימיים לכתובות שמפנות (301/308)</t>
-        </is>
-      </c>
-      <c r="I62" s="2" t="inlineStr">
-        <is>
-          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). קישור פנימי לכתובת שמפנה (301). לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
-        </is>
-      </c>
-      <c r="J62" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="K62" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/טסט-5/javaScript(0</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="n">
-        <v>301</v>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>301 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D63" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F63" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t>קישורים פנימיים לכתובות שמפנות (301/308)</t>
-        </is>
-      </c>
-      <c r="I63" s="2" t="inlineStr">
-        <is>
-          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). קישור פנימי לכתובת שמפנה (301). לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
-        </is>
-      </c>
-      <c r="J63" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="K63" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/טסט-6/javaScript(0</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="n">
-        <v>301</v>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>301 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D64" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F64" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>קישורים פנימיים לכתובות שמפנות (301/308)</t>
-        </is>
-      </c>
-      <c r="I64" s="2" t="inlineStr">
-        <is>
-          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). קישור פנימי לכתובת שמפנה (301). לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
-        </is>
-      </c>
-      <c r="J64" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="K64" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://talentsolutions.manpowergroup.co.il/manageandoptimize/ </t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="n">
-        <v>301</v>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>301 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D65" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/manageandoptimize/</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F65" s="2" t="n">
-        <v>79</v>
-      </c>
-      <c r="G65" s="6" t="inlineStr">
+        <v>78</v>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
         <is>
           <t>https://talentsolutions.manpowergroup.co.il/
 https://talentsolutions.manpowergroup.co.il/contact/
@@ -4364,187 +2499,24 @@
 (ועוד 29)</t>
         </is>
       </c>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>קישורים פנימיים ללא לוכסן סופי</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr">
-        <is>
-          <t>הקישור מכיל רווח בסוף הכתובת, והשרת מפנה לכתובת ללא הרווח. לתקן את הקישור בעמודי המקור.</t>
-        </is>
-      </c>
-      <c r="J65" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/manageandoptimize/</t>
-        </is>
-      </c>
-      <c r="K65" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/blog</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="n">
-        <v>301</v>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>301 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D66" s="6" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>קישור פנימי לכתובת ללא לוכסן סופי (או עם), שמפנה לגרסה הקנונית. לעדכן את הקישור לכתובת היעד.</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
         <is>
           <t>https://talentsolutions.manpowergroup.co.il/blog/</t>
         </is>
       </c>
-      <c r="E66" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F66" s="2" t="n">
-        <v>78</v>
-      </c>
-      <c r="G66" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/
-https://talentsolutions.manpowergroup.co.il/contact/
-https://talentsolutions.manpowergroup.co.il/about-us/
-https://talentsolutions.manpowergroup.co.il/rod-מול-end-to-end-rpo-איך-לבחור-את-המודל-הנכון-לארגו/
-https://talentsolutions.manpowergroup.co.il/transform/
-https://talentsolutions.manpowergroup.co.il/manageandoptimize/organizationalconsulting/
-https://talentsolutions.manpowergroup.co.il/manageandoptimize/operationalexcellence/
-https://talentsolutions.manpowergroup.co.il/manageandoptimize/
-https://talentsolutions.manpowergroup.co.il/תנאי-שימוש/
-https://talentsolutions.manpowergroup.co.il/attract/rod/
-(ועוד 29)</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>קישורים פנימיים ללא לוכסן סופי</t>
-        </is>
-      </c>
-      <c r="I66" s="2" t="inlineStr">
-        <is>
-          <t>קישור פנימי לכתובת ללא לוכסן סופי (או עם), שמפנה לגרסה הקנונית. לעדכן את הקישור לכתובת היעד.</t>
-        </is>
-      </c>
-      <c r="J66" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/blog/</t>
-        </is>
-      </c>
-      <c r="K66" s="4" t="inlineStr">
+      <c r="K25" s="4" t="inlineStr">
         <is>
           <t>בינונית</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/market-intelligence/ ‎</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="n">
-        <v>301</v>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>301 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D67" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F67" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G67" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/attract/</t>
-        </is>
-      </c>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t>קישורים פנימיים ללא לוכסן סופי</t>
-        </is>
-      </c>
-      <c r="I67" s="2" t="inlineStr">
-        <is>
-          <t>הקישור מכיל רווח בסוף הכתובת, והשרת מפנה לכתובת ללא הרווח. לתקן את הקישור בעמודי המקור.</t>
-        </is>
-      </c>
-      <c r="J67" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="K67" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://talentsolutions.manpowergroup.co.il/rpo-projects/ </t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="n">
-        <v>301</v>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>301 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D68" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/attract/rpo-projects/</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F68" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G68" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/attract/</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>קישורים פנימיים ללא לוכסן סופי</t>
-        </is>
-      </c>
-      <c r="I68" s="2" t="inlineStr">
-        <is>
-          <t>הקישור מכיל רווח בסוף הכתובת, והשרת מפנה לכתובת ללא הרווח. לתקן את הקישור בעמודי המקור.</t>
-        </is>
-      </c>
-      <c r="J68" s="6" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/attract/rpo-projects/</t>
-        </is>
-      </c>
-      <c r="K68" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
         </is>
       </c>
     </row>
@@ -4664,7 +2636,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>קישורי Cloudflare (ללא טיפול)</t>
+          <t>קישורים ללא צורך בטיפול (Cloudflare, הפניות לדומיין חיצוני)</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">

--- a/public/crawlability-talentsolutions-september-2026.xlsx
+++ b/public/crawlability-talentsolutions-september-2026.xlsx
@@ -654,7 +654,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>כתובות שבורות (404): כתובת אחת (הבולטת: https://talentsolutions.manpowergroup.co.il/wp-content/uploads/2022/07/אורנה_2_פ…, 0 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>כתובות שבורות (404): כתובת אחת (הבולטת: https://talentsolutions.manpowergroup.co.il/wp-content/uploads/2022/07/אורנה_2_פ…, עמוד מקור אחד). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>שרשרת של 2 הפניות. להגדיר הפניה ישירה ליעד הסופי ולעדכן את הקישורים הפנימיים אליו.</t>
+          <t>הכתובת מפנה לעמוד הבית: העמוד המקורי הוסר. לשחזר את העמוד או לעדכן את הקישור לעמוד רלוונטי; אין להשאיר קישורים שמובילים לעמוד הבית דרך הפניה.</t>
         </is>
       </c>
       <c r="J4" s="6" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>שרשרת של 3 הפניות. להגדיר הפניה ישירה ליעד הסופי ולעדכן את הקישורים הפנימיים אליו.</t>
+          <t>הכתובת מפנה לעמוד הבית: העמוד המקורי הוסר. לשחזר את העמוד או לעדכן את הקישור לעמוד רלוונטי; אין להשאיר קישורים שמובילים לעמוד הבית דרך הפניה.</t>
         </is>
       </c>
       <c r="J5" s="6" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>הפניה זמנית (302) לעמוד קיים. להמיר להפניית 301 ליעד ולעדכן את הקישורים הפנימיים ישירות ליעד.</t>
+          <t>הפניה זמנית (302) לעמוד קיים. אם ההפניה מכוונת וקבועה, להמיר להפניית 301 ליעד ולעדכן את הקישורים הפנימיים ישירות ליעד; אם הכתובת המקורית אמורה לחזור, לבטל את ההפניה.</t>
         </is>
       </c>
       <c r="J6" s="6" t="inlineStr">
@@ -1517,7 +1517,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>קישור פנימי לכתובת שמפנה (301). לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
+          <t>הכתובת מפנה לעמוד הבית: העמוד המקורי הוסר. לשחזר את העמוד או לעדכן את הקישור לעמוד רלוונטי; אין להשאיר קישורים שמובילים לעמוד הבית דרך הפניה.</t>
         </is>
       </c>
       <c r="J6" s="6" t="inlineStr">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>קישור פנימי לכתובת שמפנה (301). לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
+          <t>הכתובת מפנה לעמוד הבית: העמוד המקורי הוסר. לשחזר את העמוד או לעדכן את הקישור לעמוד רלוונטי; אין להשאיר קישורים שמובילים לעמוד הבית דרך הפניה.</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>קישור פנימי לכתובת שמפנה (301). לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
+          <t>הכתובת מפנה לעמוד הבית: העמוד המקורי הוסר. לשחזר את העמוד או לעדכן את הקישור לעמוד רלוונטי; אין להשאיר קישורים שמובילים לעמוד הבית דרך הפניה.</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>קישור פנימי לכתובת שמפנה (301). לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
+          <t>הכתובת מפנה לעמוד הבית: העמוד המקורי הוסר. לשחזר את העמוד או לעדכן את הקישור לעמוד רלוונטי; אין להשאיר קישורים שמובילים לעמוד הבית דרך הפניה.</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>קישור פנימי לכתובת שמפנה (301). לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
+          <t>הכתובת מפנה לעמוד הבית: העמוד המקורי הוסר. לשחזר את העמוד או לעדכן את הקישור לעמוד רלוונטי; אין להשאיר קישורים שמובילים לעמוד הבית דרך הפניה.</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>קישור פנימי לכתובת שמפנה (301). לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
+          <t>הכתובת מפנה לעמוד הבית: העמוד המקורי הוסר. לשחזר את העמוד או לעדכן את הקישור לעמוד רלוונטי; אין להשאיר קישורים שמובילים לעמוד הבית דרך הפניה.</t>
         </is>
       </c>
       <c r="J22" s="6" t="inlineStr">

--- a/public/crawlability-talentsolutions-september-2026.xlsx
+++ b/public/crawlability-talentsolutions-september-2026.xlsx
@@ -519,7 +519,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>לולאות הפניה: 2 כתובות (הבולטת: https://talentsolutions.manpowergroup.co.il/careers/, 39 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>לולאות הפניה: 2 כתובות; הבולטת https://talentsolutions.manpowergroup.co.il/careers/ (39 קישורים נכנסים).</t>
         </is>
       </c>
     </row>
@@ -549,7 +549,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>קישורים שגויים בתבנית (javaScript(0);): 78 כתובות (הבולטת: https://talentsolutions.manpowergroup.co.il/javaScript(0);, 4 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>קישורים שגויים בתבנית (javaScript(0);): 78 כתובות; הבולטת https://talentsolutions.manpowergroup.co.il/javaScript(0); (4 קישורים נכנסים).</t>
         </is>
       </c>
     </row>
@@ -564,7 +564,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>קישורים עם רווח בסוף הכתובת: 3 כתובות (הבולטת: https://talentsolutions.manpowergroup.co.il/manageandoptimize/ [רווח בסוף], 79 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>קישורים עם רווח בסוף הכתובת: 3 כתובות; הבולטת https://talentsolutions.manpowergroup.co.il/manageandoptimize/ [רווח בסוף] (79 קישורים נכנסים).</t>
         </is>
       </c>
     </row>
@@ -579,7 +579,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>שרשראות הפניות: 2 כתובות (הבולטת: https://talentsolutions.manpowergroup.co.il/retainanddevelop/outplacement/, 196 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>שרשראות הפניות: 2 כתובות; הבולטת https://talentsolutions.manpowergroup.co.il/retainanddevelop/outplacement/ (196 קישורים נכנסים).</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>הפניות זמניות (302/307): כתובת אחת (הבולטת: https://talentsolutions.manpowergroup.co.il/contact/?lang=he, 3 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>הפניות זמניות (302/307): כתובת אחת; הבולטת https://talentsolutions.manpowergroup.co.il/contact/?lang=he (3 קישורים נכנסים).</t>
         </is>
       </c>
     </row>
@@ -609,7 +609,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>קישורים פנימיים לכתובות שמפנות (301/308): 23 כתובות (הבולטת: https://talentsolutions.manpowergroup.co.il/operationalexcellence/, 80 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>קישורים פנימיים לכתובות שמפנות (301/308): 23 כתובות; הבולטת https://talentsolutions.manpowergroup.co.il/operationalexcellence/ (80 קישורים נכנסים).</t>
         </is>
       </c>
     </row>
@@ -624,7 +624,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>קישורים פנימיים ללא לוכסן סופי: כתובת אחת (הבולטת: https://talentsolutions.manpowergroup.co.il/blog, 78 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>קישורים פנימיים ללא לוכסן סופי: כתובת אחת; הבולטת https://talentsolutions.manpowergroup.co.il/blog (78 קישורים נכנסים).</t>
         </is>
       </c>
     </row>
@@ -654,7 +654,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>כתובות שבורות (404): כתובת אחת (הבולטת: https://talentsolutions.manpowergroup.co.il/wp-content/uploads/2022/07/אורנה_2_פ…, עמוד מקור אחד). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>כתובות שבורות (404): כתובת אחת; הבולטת https://talentsolutions.manpowergroup.co.il/wp-content/uploads/2022/07/אורנה_2_פ… (עמוד מקור אחד).</t>
         </is>
       </c>
     </row>
@@ -669,7 +669,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>להריץ מחדש את ה-Website Audit של talentsolutions ב-SE Ranking (הסריקה האחרונה: 2026-05-25); הפעלה מחדש דרך ה-API אינה זמינה בחשבון, יש להפעיל בממשק.</t>
+          <t>להריץ מחדש (בממשק) את ה-Website Audit של talentsolutions ב-SE Ranking; הסריקה האחרונה: 2026-05-25.</t>
         </is>
       </c>
     </row>
@@ -2531,7 +2531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -2607,25 +2607,72 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
+          <t>https://talentsolutions.manpowergroup.co.il/?page_id=1212</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>301 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>כתובות מפנות ללא קישור פנימי שאותר</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). אין פעולה בקישורים; אם יאותר מקור, לעדכן אותו לכתובת היעד.</t>
+        </is>
+      </c>
+      <c r="J2" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
           <t>https://talentsolutions.manpowergroup.co.il/cdn-cgi/l/email-protection</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B3" s="2" t="n">
         <v>404</v>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>404</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="n">
+      <c r="D3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F3" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>https://talentsolutions.manpowergroup.co.il/contact/
 https://talentsolutions.manpowergroup.co.il/about-us/
@@ -2634,18 +2681,18 @@
 https://talentsolutions.manpowergroup.co.il/מדיניות-פרטיות/</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>קישורים ללא צורך בטיפול (Cloudflare, הפניות לדומיין חיצוני)</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>קישור הגנת דוא"ל של Cloudflare (cdn-cgi). גוגל מתעלם מכתובות cdn-cgi; לא נדרש טיפול. ניתן לבטל את Email Address Obfuscation ב-Cloudflare כדי שהסורקים לא ידווחו על כך.</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="5" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>נמוכה</t>
         </is>

--- a/public/crawlability-talentsolutions-september-2026.xlsx
+++ b/public/crawlability-talentsolutions-september-2026.xlsx
@@ -13,8 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="קישורים להפניות 301" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ללא טיפול" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="robots, sitemap, אינדוקס" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="תת-דומיינים" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="מקורות" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="מקורות" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -468,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -527,14 +526,14 @@
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>גבוהה</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>5 כתובות במפת האתר חסומות ב-robots.txt; להסיר מהמפה או לפתוח לסריקה.</t>
+          <t>שרשראות הפניות: 2 כתובות; הבולטת https://talentsolutions.manpowergroup.co.il/retainanddevelop/outplacement/ (196 קישורים נכנסים).</t>
         </is>
       </c>
     </row>
@@ -549,7 +548,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>קישורים שגויים בתבנית (javaScript(0);): 78 כתובות; הבולטת https://talentsolutions.manpowergroup.co.il/javaScript(0); (4 קישורים נכנסים).</t>
+          <t>5 כתובות במפת האתר חסומות ב-robots.txt; להסיר מהמפה או לפתוח לסריקה.</t>
         </is>
       </c>
     </row>
@@ -564,7 +563,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>קישורים עם רווח בסוף הכתובת: 3 כתובות; הבולטת https://talentsolutions.manpowergroup.co.il/manageandoptimize/ [רווח בסוף] (79 קישורים נכנסים).</t>
+          <t>קישורים שגויים בתבנית (javaScript(0);): 78 כתובות; הבולטת https://talentsolutions.manpowergroup.co.il/javaScript(0); (4 קישורים נכנסים).</t>
         </is>
       </c>
     </row>
@@ -579,7 +578,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>שרשראות הפניות: 2 כתובות; הבולטת https://talentsolutions.manpowergroup.co.il/retainanddevelop/outplacement/ (196 קישורים נכנסים).</t>
+          <t>קישורים עם רווח בסוף הכתובת: 3 כתובות; הבולטת https://talentsolutions.manpowergroup.co.il/manageandoptimize/ [רווח בסוף] (79 קישורים נכנסים).</t>
         </is>
       </c>
     </row>
@@ -639,37 +638,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>quest.manpowergroup.co.il: להגדיר noindex (כתובת אחת באינדקס).</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
           <t>כתובות שבורות (404): כתובת אחת; הבולטת https://talentsolutions.manpowergroup.co.il/wp-content/uploads/2022/07/אורנה_2_פ… (עמוד מקור אחד).</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>להריץ מחדש (בממשק) את ה-Website Audit של talentsolutions ב-SE Ranking; הסריקה האחרונה: 2026-05-25.</t>
         </is>
       </c>
     </row>
@@ -1039,9 +1008,9 @@
           <t>https://talentsolutions.manpowergroup.co.il/</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>גבוהה</t>
         </is>
       </c>
     </row>
@@ -3317,117 +3286,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="45" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="70" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>תת-דומיין</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>קוד</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>כותרת</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>meta robots</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>canonical</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>כתובות באינדקס (site:)</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>סיווג</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>פעולה</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>עדיפות</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>quest.manpowergroup.co.il</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>מערכת שאלונים - דף כניסה</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>מערכת שאלונים</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>להגדיר noindex (כתובת אחת באינדקס).</t>
-        </is>
-      </c>
-      <c r="I2" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/public/crawlability-talentsolutions-september-2026.xlsx
+++ b/public/crawlability-talentsolutions-september-2026.xlsx
@@ -42,7 +42,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -69,6 +69,11 @@
         <fgColor rgb="00E2E3E5"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D4EDDA"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -82,7 +87,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -101,6 +106,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -563,7 +571,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>קישורים שגויים בתבנית (javaScript(0);): 78 כתובות; הבולטת https://talentsolutions.manpowergroup.co.il/javaScript(0); (4 קישורים נכנסים).</t>
+          <t>קישורים שגויים בתבנית (javaScript(0);): 39 כתובות; הבולטת https://talentsolutions.manpowergroup.co.il/javaScript(0); (4 קישורים נכנסים).</t>
         </is>
       </c>
     </row>
@@ -900,7 +908,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>לולאת הפניות: הכתובת מפנה לעצמה. לבטל את כלל ההפניה הכפול או להגדיר יעד סופי תקין.</t>
+          <t>לולאת הפניות בין הכתובת ל-https://talentsolutions.manpowergroup.co.il/careers/?lang=en: כל אחת מפנה לשנייה. לבטל את אחת ההפניות.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
@@ -943,7 +951,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>לולאת הפניות: הכתובת מפנה לעצמה. לבטל את כלל ההפניה הכפול או להגדיר יעד סופי תקין.</t>
+          <t>לולאת הפניות בין הכתובת ל-https://talentsolutions.manpowergroup.co.il/careers/: כל אחת מפנה לשנייה. לבטל את אחת ההפניות.</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
@@ -2500,7 +2508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -2664,6 +2672,1683 @@
       <c r="K3" s="5" t="inlineStr">
         <is>
           <t>נמוכה</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/javaScript(0</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>301 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>קישורים ללא צורך בטיפול (Cloudflare, הפניות לדומיין חיצוני)</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>כתובת ביניים של ההפניה מהקישור השגוי javaScript(0); נפתרת עם תיקון התבנית.</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="7" t="inlineStr">
+        <is>
+          <t>ללא</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/contact/javaScript(0</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>301 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>קישורים ללא צורך בטיפול (Cloudflare, הפניות לדומיין חיצוני)</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>כתובת ביניים של ההפניה מהקישור השגוי javaScript(0); נפתרת עם תיקון התבנית.</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="7" t="inlineStr">
+        <is>
+          <t>ללא</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/about-us/javaScript(0</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>301 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>קישורים ללא צורך בטיפול (Cloudflare, הפניות לדומיין חיצוני)</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>כתובת ביניים של ההפניה מהקישור השגוי javaScript(0); נפתרת עם תיקון התבנית.</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="7" t="inlineStr">
+        <is>
+          <t>ללא</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/rod-מול-end-to-end-rpo-איך-לבחור-את-המודל-הנכון-לארגו/javaScript(0</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>301 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>קישורים ללא צורך בטיפול (Cloudflare, הפניות לדומיין חיצוני)</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>כתובת ביניים של ההפניה מהקישור השגוי javaScript(0); נפתרת עם תיקון התבנית.</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="7" t="inlineStr">
+        <is>
+          <t>ללא</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/transform/javaScript(0</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>301 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>קישורים ללא צורך בטיפול (Cloudflare, הפניות לדומיין חיצוני)</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>כתובת ביניים של ההפניה מהקישור השגוי javaScript(0); נפתרת עם תיקון התבנית.</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="7" t="inlineStr">
+        <is>
+          <t>ללא</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/manageandoptimize/organizationalconsulting/javaScript(0</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>301 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>קישורים ללא צורך בטיפול (Cloudflare, הפניות לדומיין חיצוני)</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>כתובת ביניים של ההפניה מהקישור השגוי javaScript(0); נפתרת עם תיקון התבנית.</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="7" t="inlineStr">
+        <is>
+          <t>ללא</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/manageandoptimize/javaScript(0</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>301 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>קישורים ללא צורך בטיפול (Cloudflare, הפניות לדומיין חיצוני)</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>כתובת ביניים של ההפניה מהקישור השגוי javaScript(0); נפתרת עם תיקון התבנית.</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="7" t="inlineStr">
+        <is>
+          <t>ללא</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/manageandoptimize/operationalexcellence/javaScript(0</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>301 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>קישורים ללא צורך בטיפול (Cloudflare, הפניות לדומיין חיצוני)</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>כתובת ביניים של ההפניה מהקישור השגוי javaScript(0); נפתרת עם תיקון התבנית.</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="7" t="inlineStr">
+        <is>
+          <t>ללא</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/attract/rod/javaScript(0</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>301 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>קישורים ללא צורך בטיפול (Cloudflare, הפניות לדומיין חיצוני)</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>כתובת ביניים של ההפניה מהקישור השגוי javaScript(0); נפתרת עם תיקון התבנית.</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="7" t="inlineStr">
+        <is>
+          <t>ללא</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/attract/rpo/javaScript(0</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>301 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>קישורים ללא צורך בטיפול (Cloudflare, הפניות לדומיין חיצוני)</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>כתובת ביניים של ההפניה מהקישור השגוי javaScript(0); נפתרת עם תיקון התבנית.</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="7" t="inlineStr">
+        <is>
+          <t>ללא</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/תנאי-שימוש/javaScript(0</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>301 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>קישורים ללא צורך בטיפול (Cloudflare, הפניות לדומיין חיצוני)</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>כתובת ביניים של ההפניה מהקישור השגוי javaScript(0); נפתרת עם תיקון התבנית.</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="7" t="inlineStr">
+        <is>
+          <t>ללא</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/מדיניות-קוקיז/javaScript(0</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>301 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>קישורים ללא צורך בטיפול (Cloudflare, הפניות לדומיין חיצוני)</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>כתובת ביניים של ההפניה מהקישור השגוי javaScript(0); נפתרת עם תיקון התבנית.</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="7" t="inlineStr">
+        <is>
+          <t>ללא</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/ibm/javaScript(0</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>301 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>קישורים ללא צורך בטיפול (Cloudflare, הפניות לדומיין חיצוני)</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>כתובת ביניים של ההפניה מהקישור השגוי javaScript(0); נפתרת עם תיקון התבנית.</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="7" t="inlineStr">
+        <is>
+          <t>ללא</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/מדיניות-פרטיות/javaScript(0</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>301 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>קישורים ללא צורך בטיפול (Cloudflare, הפניות לדומיין חיצוני)</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>כתובת ביניים של ההפניה מהקישור השגוי javaScript(0); נפתרת עם תיקון התבנית.</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="7" t="inlineStr">
+        <is>
+          <t>ללא</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/retainanddevelop/javaScript(0</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>301 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>קישורים ללא צורך בטיפול (Cloudflare, הפניות לדומיין חיצוני)</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>כתובת ביניים של ההפניה מהקישור השגוי javaScript(0); נפתרת עם תיקון התבנית.</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="7" t="inlineStr">
+        <is>
+          <t>ללא</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/מה-זה-rpo-ב-60-שניות/javaScript(0</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>301 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>קישורים ללא צורך בטיפול (Cloudflare, הפניות לדומיין חיצוני)</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>כתובת ביניים של ההפניה מהקישור השגוי javaScript(0); נפתרת עם תיקון התבנית.</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="7" t="inlineStr">
+        <is>
+          <t>ללא</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/attract/market-intelligence/javaScript(0</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>301 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>קישורים ללא צורך בטיפול (Cloudflare, הפניות לדומיין חיצוני)</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>כתובת ביניים של ההפניה מהקישור השגוי javaScript(0); נפתרת עם תיקון התבנית.</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="7" t="inlineStr">
+        <is>
+          <t>ללא</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/retainanddevelop/developmentprograms/javaScript(0</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>301 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>קישורים ללא צורך בטיפול (Cloudflare, הפניות לדומיין חיצוני)</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>כתובת ביניים של ההפניה מהקישור השגוי javaScript(0); נפתרת עם תיקון התבנית.</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="7" t="inlineStr">
+        <is>
+          <t>ללא</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/about-us/msp/javaScript(0</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>301 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>קישורים ללא צורך בטיפול (Cloudflare, הפניות לדומיין חיצוני)</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>כתובת ביניים של ההפניה מהקישור השגוי javaScript(0); נפתרת עם תיקון התבנית.</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="7" t="inlineStr">
+        <is>
+          <t>ללא</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/ministry/javaScript(0</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>301 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>קישורים ללא צורך בטיפול (Cloudflare, הפניות לדומיין חיצוני)</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>כתובת ביניים של ההפניה מהקישור השגוי javaScript(0); נפתרת עם תיקון התבנית.</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="7" t="inlineStr">
+        <is>
+          <t>ללא</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/attract/javaScript(0</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>301 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>קישורים ללא צורך בטיפול (Cloudflare, הפניות לדומיין חיצוני)</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>כתובת ביניים של ההפניה מהקישור השגוי javaScript(0); נפתרת עם תיקון התבנית.</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="7" t="inlineStr">
+        <is>
+          <t>ללא</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/mistakes/javaScript(0</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>301 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>קישורים ללא צורך בטיפול (Cloudflare, הפניות לדומיין חיצוני)</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>כתובת ביניים של ההפניה מהקישור השגוי javaScript(0); נפתרת עם תיקון התבנית.</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="7" t="inlineStr">
+        <is>
+          <t>ללא</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/blog/javaScript(0</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>301 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>קישורים ללא צורך בטיפול (Cloudflare, הפניות לדומיין חיצוני)</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>כתובת ביניים של ההפניה מהקישור השגוי javaScript(0); נפתרת עם תיקון התבנית.</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="7" t="inlineStr">
+        <is>
+          <t>ללא</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/transform/professionaldevelopment/javaScript(0</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>301 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>קישורים ללא צורך בטיפול (Cloudflare, הפניות לדומיין חיצוני)</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>כתובת ביניים של ההפניה מהקישור השגוי javaScript(0); נפתרת עם תיקון התבנית.</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="7" t="inlineStr">
+        <is>
+          <t>ללא</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/טסט-8/javaScript(0</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>301 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>קישורים ללא צורך בטיפול (Cloudflare, הפניות לדומיין חיצוני)</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>כתובת ביניים של ההפניה מהקישור השגוי javaScript(0); נפתרת עם תיקון התבנית.</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="7" t="inlineStr">
+        <is>
+          <t>ללא</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/אתגרים-בגיוס-טאלנטים-להייטק-בישראל/javaScript(0</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>301 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>קישורים ללא צורך בטיפול (Cloudflare, הפניות לדומיין חיצוני)</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>כתובת ביניים של ההפניה מהקישור השגוי javaScript(0); נפתרת עם תיקון התבנית.</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="7" t="inlineStr">
+        <is>
+          <t>ללא</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/blog/page/2/javaScript(0</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>301 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>קישורים ללא צורך בטיפול (Cloudflare, הפניות לדומיין חיצוני)</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>כתובת ביניים של ההפניה מהקישור השגוי javaScript(0); נפתרת עם תיקון התבנית.</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="7" t="inlineStr">
+        <is>
+          <t>ללא</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/היתרונות-של-מיקור-החוץ-בתהליכי-גיוס/javaScript(0</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>301 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>קישורים ללא צורך בטיפול (Cloudflare, הפניות לדומיין חיצוני)</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>כתובת ביניים של ההפניה מהקישור השגוי javaScript(0); נפתרת עם תיקון התבנית.</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="7" t="inlineStr">
+        <is>
+          <t>ללא</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/attract/rpo-projects/javaScript(0</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>301 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>קישורים ללא צורך בטיפול (Cloudflare, הפניות לדומיין חיצוני)</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>כתובת ביניים של ההפניה מהקישור השגוי javaScript(0); נפתרת עם תיקון התבנית.</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="7" t="inlineStr">
+        <is>
+          <t>ללא</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/category/ללא-קטגוריה/javaScript(0</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>301 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>קישורים ללא צורך בטיפול (Cloudflare, הפניות לדומיין חיצוני)</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>כתובת ביניים של ההפניה מהקישור השגוי javaScript(0); נפתרת עם תיקון התבנית.</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="7" t="inlineStr">
+        <is>
+          <t>ללא</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/team/jonas-prising-6/javaScript(0</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>301 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>קישורים ללא צורך בטיפול (Cloudflare, הפניות לדומיין חיצוני)</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>כתובת ביניים של ההפניה מהקישור השגוי javaScript(0); נפתרת עם תיקון התבנית.</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="7" t="inlineStr">
+        <is>
+          <t>ללא</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/team/אינה-סרנגה/javaScript(0</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>301 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>קישורים ללא צורך בטיפול (Cloudflare, הפניות לדומיין חיצוני)</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>כתובת ביניים של ההפניה מהקישור השגוי javaScript(0); נפתרת עם תיקון התבנית.</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="7" t="inlineStr">
+        <is>
+          <t>ללא</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/team/אלכסנדרה-ויט/javaScript(0</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>301 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>קישורים ללא צורך בטיפול (Cloudflare, הפניות לדומיין חיצוני)</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>כתובת ביניים של ההפניה מהקישור השגוי javaScript(0); נפתרת עם תיקון התבנית.</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="7" t="inlineStr">
+        <is>
+          <t>ללא</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/team/jonas-prising-7/javaScript(0</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>301 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>קישורים ללא צורך בטיפול (Cloudflare, הפניות לדומיין חיצוני)</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>כתובת ביניים של ההפניה מהקישור השגוי javaScript(0); נפתרת עם תיקון התבנית.</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="7" t="inlineStr">
+        <is>
+          <t>ללא</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/team/jonas-prising-8/javaScript(0</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>301 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>קישורים ללא צורך בטיפול (Cloudflare, הפניות לדומיין חיצוני)</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>כתובת ביניים של ההפניה מהקישור השגוי javaScript(0); נפתרת עם תיקון התבנית.</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="7" t="inlineStr">
+        <is>
+          <t>ללא</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/category/ללא-קטגוריה/page/2/javaScript(0</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>301 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>קישורים ללא צורך בטיפול (Cloudflare, הפניות לדומיין חיצוני)</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>כתובת ביניים של ההפניה מהקישור השגוי javaScript(0); נפתרת עם תיקון התבנית.</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="7" t="inlineStr">
+        <is>
+          <t>ללא</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/טסט-4/javaScript(0</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>301 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>קישורים ללא צורך בטיפול (Cloudflare, הפניות לדומיין חיצוני)</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>כתובת ביניים של ההפניה מהקישור השגוי javaScript(0); נפתרת עם תיקון התבנית.</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="7" t="inlineStr">
+        <is>
+          <t>ללא</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/טסט-5/javaScript(0</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>301 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>קישורים ללא צורך בטיפול (Cloudflare, הפניות לדומיין חיצוני)</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>כתובת ביניים של ההפניה מהקישור השגוי javaScript(0); נפתרת עם תיקון התבנית.</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="7" t="inlineStr">
+        <is>
+          <t>ללא</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/טסט-6/javaScript(0</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>301 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>קישורים ללא צורך בטיפול (Cloudflare, הפניות לדומיין חיצוני)</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>כתובת ביניים של ההפניה מהקישור השגוי javaScript(0); נפתרת עם תיקון התבנית.</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="7" t="inlineStr">
+        <is>
+          <t>ללא</t>
         </is>
       </c>
     </row>
